--- a/tame_output/ON/bt/strategyON_20230826.xlsx
+++ b/tame_output/ON/bt/strategyON_20230826.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-158.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.2%</t>
+          <t>133.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1700"/>
+  <dimension ref="A1:G1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40610,7 +40610,7 @@
         <v>45162</v>
       </c>
       <c r="B1700" t="n">
-        <v>2.768728818568964</v>
+        <v>2.770543733547061</v>
       </c>
       <c r="C1700" t="n">
         <v>2.89581178561028</v>
@@ -40626,6 +40626,29 @@
       </c>
       <c r="G1700" t="n">
         <v>4.193394308794908</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="2" t="n">
+        <v>45163</v>
+      </c>
+      <c r="B1701" t="n">
+        <v>2.770093262391005</v>
+      </c>
+      <c r="C1701" t="n">
+        <v>2.897971724056924</v>
+      </c>
+      <c r="D1701" t="n">
+        <v>1.541798885481946</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>3.514334853935956</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>2.162386897628392</v>
+      </c>
+      <c r="G1701" t="n">
+        <v>4.19540386263396</v>
       </c>
     </row>
   </sheetData>
